--- a/mit_readme.xlsx
+++ b/mit_readme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavol\Desktop\Škola\mit_projekty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76B655F-8393-4A4C-8910-255691EA7E81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8AB4E2A-076D-4971-B3F9-F1ADCDB32820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16896" xr2:uid="{C8937BAE-C9A4-4CEB-A19F-3DAEC926D725}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="98">
   <si>
     <t>Predmet</t>
   </si>
@@ -301,13 +301,31 @@
   </si>
   <si>
     <t>ZPO - Image Processing</t>
+  </si>
+  <si>
+    <t>Akcelerační datové struktury pro ray-tracing</t>
+  </si>
+  <si>
+    <t>Prezentace pěkná, projekt funkční, dokumentace splněna, podpora interaktivní editace scén, denoiserů a optimalizací.</t>
+  </si>
+  <si>
+    <t>31 / 31</t>
+  </si>
+  <si>
+    <t>26 / 29</t>
+  </si>
+  <si>
+    <t>Autor v rámci projektu úspěšně realizoval různé interpolační metody pro úlohu rotace obrazu, přičemž prokázal schopnost tyto metody vhodně a objektivně vyhodnotit s využitím relevantních metrik. Projekt je zpracován velmi pečlivě a svou odbornou kvalitou i celkovým rozsahem představuje mírně nadprůměrnou práci. Velmi oceňuji také propracované grafické uživatelské rozhraní (GUI), které slouží jako výborný nástroj pro názornou demonstraci a srovnání vlivu jednotlivých metod. Tato kombinace technické realizace a vizualizace dává projektu ucelený charakter. Jako inspiraci pro další profesionální růst doporučuji u budoucích projektů doplnit o něco detailnější komentáře přímo do zdrojových kódů, což by ještě více usnadnilo orientaci v jejich struktuře a podpořilo jejich další rozšiřitelnost. Celkově se jedná o velmi zdařilé a funkční řešení.</t>
+  </si>
+  <si>
+    <t>Rotace obrazu</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,6 +351,13 @@
       <charset val="238"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -901,9 +926,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1006,16 +1028,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1026,6 +1044,15 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1343,20 +1370,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C58E8B0-51CD-4485-AAB7-F2F9933D37DC}">
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.77734375" customWidth="1"/>
-    <col min="2" max="2" width="49.109375" customWidth="1"/>
-    <col min="3" max="3" width="38.77734375" customWidth="1"/>
-    <col min="4" max="4" width="49.109375" customWidth="1"/>
-    <col min="5" max="5" width="37.77734375" customWidth="1"/>
-    <col min="6" max="6" width="255.77734375" customWidth="1"/>
+    <col min="1" max="1" width="11.21875" style="48" customWidth="1"/>
+    <col min="2" max="2" width="49.109375" style="48" customWidth="1"/>
+    <col min="3" max="3" width="38.77734375" style="48" customWidth="1"/>
+    <col min="4" max="4" width="52.109375" style="48" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" style="48" customWidth="1"/>
+    <col min="6" max="6" width="255.77734375" style="54" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="48"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="2" spans="1:6" ht="15.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="17" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="12" t="s">
@@ -1371,30 +1399,30 @@
       <c r="E2" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="14" t="s">
+      <c r="F2" s="55" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="18">
         <v>1</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="34"/>
+      <c r="F3" s="33"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="23"/>
+      <c r="A4" s="22"/>
       <c r="B4" s="3"/>
       <c r="C4" s="8">
         <v>2</v>
@@ -1405,10 +1433,10 @@
       <c r="E4" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="35"/>
+      <c r="F4" s="34"/>
     </row>
     <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="21"/>
+      <c r="A5" s="20"/>
       <c r="B5" s="9"/>
       <c r="C5" s="10">
         <v>3</v>
@@ -1419,19 +1447,19 @@
       <c r="E5" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="36"/>
+      <c r="F5" s="35"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
-      <c r="B6" s="15"/>
+      <c r="B6" s="14"/>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
-      <c r="F6" s="37"/>
+      <c r="F6" s="36"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>14</v>
       </c>
       <c r="C7" s="8" t="s">
@@ -1443,13 +1471,13 @@
       <c r="E7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="38" t="s">
+      <c r="F7" s="37" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
-      <c r="B8" s="16"/>
+      <c r="B8" s="15"/>
       <c r="C8" s="8" t="s">
         <v>16</v>
       </c>
@@ -1459,13 +1487,13 @@
       <c r="E8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="38" t="s">
+      <c r="F8" s="37" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="5"/>
-      <c r="B9" s="17"/>
+      <c r="B9" s="16"/>
       <c r="C9" s="10" t="s">
         <v>17</v>
       </c>
@@ -1475,38 +1503,38 @@
       <c r="E9" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F9" s="39"/>
+      <c r="F9" s="38"/>
     </row>
     <row r="10" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="25"/>
-      <c r="B10" s="26"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="40"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="26"/>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="39"/>
     </row>
     <row r="11" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="28" t="s">
+      <c r="D11" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="19" t="s">
+      <c r="E11" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="F11" s="41" t="s">
+      <c r="F11" s="40" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="23"/>
+      <c r="A12" s="22"/>
       <c r="B12" s="9" t="s">
         <v>30</v>
       </c>
@@ -1519,40 +1547,40 @@
       <c r="E12" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="F12" s="36" t="s">
+      <c r="F12" s="35" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="29"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="42"/>
+      <c r="A13" s="28"/>
+      <c r="B13" s="25"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="41"/>
     </row>
     <row r="14" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="34" t="s">
+      <c r="F14" s="33" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="23"/>
+      <c r="A15" s="22"/>
       <c r="B15" s="9"/>
       <c r="C15" s="10" t="s">
         <v>16</v>
@@ -1563,60 +1591,60 @@
       <c r="E15" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F15" s="36" t="s">
+      <c r="F15" s="35" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="27"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="40"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="26"/>
+      <c r="D16" s="26"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="39"/>
     </row>
     <row r="17" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="21"/>
-      <c r="B17" s="30" t="s">
+      <c r="A17" s="20"/>
+      <c r="B17" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="31" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="E17" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="F17" s="43" t="s">
+      <c r="F17" s="42" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="3"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="40"/>
+      <c r="B18" s="25"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="39"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="21"/>
-      <c r="B19" s="22" t="s">
+      <c r="A19" s="20"/>
+      <c r="B19" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="19"/>
-      <c r="E19" s="20" t="s">
+      <c r="D19" s="18"/>
+      <c r="E19" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="F19" s="44"/>
+      <c r="F19" s="43"/>
     </row>
     <row r="20" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="21"/>
+      <c r="A20" s="20"/>
       <c r="B20" s="9"/>
       <c r="C20" s="10" t="s">
         <v>16</v>
@@ -1625,36 +1653,36 @@
       <c r="E20" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="45"/>
+      <c r="F20" s="44"/>
     </row>
     <row r="21" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="40"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="39"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="21"/>
-      <c r="B22" s="22" t="s">
+      <c r="A22" s="20"/>
+      <c r="B22" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="F22" s="34" t="s">
+      <c r="F22" s="33" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="33"/>
+      <c r="A23" s="32"/>
       <c r="B23" s="9"/>
       <c r="C23" s="10" t="s">
         <v>16</v>
@@ -1665,55 +1693,55 @@
       <c r="E23" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="F23" s="36" t="s">
+      <c r="F23" s="35" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="46" t="s">
+      <c r="A24" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="B24" s="47" t="s">
+      <c r="B24" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D24" s="48" t="s">
+      <c r="D24" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="E24" s="19" t="s">
+      <c r="E24" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="F24" s="34"/>
+      <c r="F24" s="33"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="2"/>
-      <c r="B25" s="16"/>
+      <c r="B25" s="15"/>
       <c r="C25" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D25" s="49" t="s">
+      <c r="D25" s="48" t="s">
         <v>60</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F25" s="35" t="s">
+      <c r="F25" s="34" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
-      <c r="B26" s="16"/>
+      <c r="B26" s="15"/>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
       <c r="E26" s="8"/>
-      <c r="F26" s="35"/>
+      <c r="F26" s="34"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C27" s="8" t="s">
@@ -1723,11 +1751,11 @@
       <c r="E27" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="F27" s="35"/>
+      <c r="F27" s="34"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
-      <c r="B28" s="16"/>
+      <c r="B28" s="15"/>
       <c r="C28" s="8" t="s">
         <v>16</v>
       </c>
@@ -1735,19 +1763,19 @@
       <c r="E28" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="F28" s="35"/>
+      <c r="F28" s="34"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
-      <c r="B29" s="16"/>
+      <c r="B29" s="15"/>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
-      <c r="F29" s="35"/>
+      <c r="F29" s="34"/>
     </row>
     <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
-      <c r="B30" s="17" t="s">
+      <c r="B30" s="16" t="s">
         <v>64</v>
       </c>
       <c r="C30" s="10" t="s">
@@ -1757,65 +1785,65 @@
       <c r="E30" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="F30" s="53" t="s">
+      <c r="F30" s="50" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="25"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="40"/>
+      <c r="A31" s="24"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="39"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="50" t="s">
+      <c r="A32" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="B32" s="47" t="s">
+      <c r="B32" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="E32" s="19" t="s">
+      <c r="E32" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="F32" s="54" t="s">
+      <c r="F32" s="51" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
-      <c r="B33" s="16"/>
+      <c r="B33" s="15"/>
       <c r="C33" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="D33" s="49" t="s">
+      <c r="D33" s="48" t="s">
         <v>71</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="F33" s="55" t="s">
+      <c r="F33" s="52" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
-      <c r="B34" s="16"/>
+      <c r="B34" s="15"/>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
-      <c r="F34" s="35"/>
+      <c r="F34" s="34"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="15" t="s">
         <v>75</v>
       </c>
       <c r="C35" s="8" t="s">
@@ -1827,45 +1855,45 @@
       <c r="E35" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="F35" s="35" t="s">
+      <c r="F35" s="34" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
-      <c r="B36" s="16"/>
+      <c r="B36" s="15"/>
       <c r="C36" s="8"/>
       <c r="D36" s="8"/>
       <c r="E36" s="8"/>
-      <c r="F36" s="35"/>
+      <c r="F36" s="34"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="15" t="s">
         <v>78</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="49" t="s">
+      <c r="D37" s="48" t="s">
         <v>79</v>
       </c>
       <c r="E37" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F37" s="35"/>
+      <c r="F37" s="34"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
-      <c r="B38" s="16"/>
+      <c r="B38" s="15"/>
       <c r="C38" s="8"/>
       <c r="D38" s="8"/>
       <c r="E38" s="8"/>
-      <c r="F38" s="35"/>
+      <c r="F38" s="34"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="15" t="s">
         <v>81</v>
       </c>
       <c r="C39" s="8" t="s">
@@ -1875,13 +1903,13 @@
       <c r="E39" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F39" s="55" t="s">
+      <c r="F39" s="52" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
-      <c r="B40" s="16"/>
+      <c r="B40" s="15"/>
       <c r="C40" s="8" t="s">
         <v>16</v>
       </c>
@@ -1889,19 +1917,19 @@
       <c r="E40" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="F40" s="35"/>
+      <c r="F40" s="34"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
-      <c r="B41" s="16"/>
+      <c r="B41" s="15"/>
       <c r="C41" s="8"/>
       <c r="D41" s="8"/>
       <c r="E41" s="8"/>
-      <c r="F41" s="35"/>
+      <c r="F41" s="34"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="15" t="s">
         <v>88</v>
       </c>
       <c r="C42" s="8" t="s">
@@ -1913,45 +1941,61 @@
       <c r="E42" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F42" s="35"/>
+      <c r="F42" s="34"/>
     </row>
     <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="5"/>
-      <c r="B43" s="17"/>
+      <c r="B43" s="16"/>
       <c r="C43" s="10"/>
       <c r="D43" s="10"/>
       <c r="E43" s="10"/>
-      <c r="F43" s="36"/>
+      <c r="F43" s="35"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="2"/>
-      <c r="B44" s="15"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="37"/>
+      <c r="A44" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="48" t="s">
+        <v>92</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="F44" s="56" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D45" s="8"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="51"/>
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="4"/>
+      <c r="F45" s="53"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
-      <c r="B46" s="4"/>
-      <c r="C46" s="4"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="56"/>
+      <c r="B46" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="4">
+        <v>1</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="E46" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F46" s="54" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
@@ -1959,19 +2003,15 @@
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
-      <c r="F47" s="56"/>
+      <c r="F47" s="53"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="4"/>
-      <c r="B48" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C48" s="4">
-        <v>1</v>
-      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
-      <c r="F48" s="56"/>
+      <c r="F48" s="53"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="4"/>
@@ -1979,7 +2019,7 @@
       <c r="C49" s="4"/>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
-      <c r="F49" s="56"/>
+      <c r="F49" s="53"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="4"/>
@@ -1987,7 +2027,7 @@
       <c r="C50" s="4"/>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
-      <c r="F50" s="56"/>
+      <c r="F50" s="53"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="4"/>
@@ -1995,7 +2035,7 @@
       <c r="C51" s="4"/>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
-      <c r="F51" s="56"/>
+      <c r="F51" s="53"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="4"/>
@@ -2003,55 +2043,39 @@
       <c r="C52" s="4"/>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
-      <c r="F52" s="56"/>
+      <c r="F52" s="53"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="52"/>
-      <c r="B53" s="52"/>
-      <c r="C53" s="52"/>
-      <c r="D53" s="52"/>
-      <c r="E53" s="52"/>
-      <c r="F53" s="52"/>
+      <c r="A53" s="4"/>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="4"/>
+      <c r="F53" s="53"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="52"/>
-      <c r="B54" s="52"/>
-      <c r="C54" s="52"/>
-      <c r="D54" s="52"/>
-      <c r="E54" s="52"/>
-      <c r="F54" s="52"/>
+      <c r="A54" s="4"/>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="4"/>
+      <c r="F54" s="53"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="52"/>
-      <c r="B55" s="52"/>
-      <c r="C55" s="52"/>
-      <c r="D55" s="52"/>
-      <c r="E55" s="52"/>
-      <c r="F55" s="52"/>
+      <c r="A55" s="4"/>
+      <c r="B55" s="4"/>
+      <c r="C55" s="4"/>
+      <c r="D55" s="4"/>
+      <c r="E55" s="4"/>
+      <c r="F55" s="53"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="52"/>
-      <c r="B56" s="52"/>
-      <c r="C56" s="52"/>
-      <c r="D56" s="52"/>
-      <c r="E56" s="52"/>
-      <c r="F56" s="52"/>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="52"/>
-      <c r="B57" s="52"/>
-      <c r="C57" s="52"/>
-      <c r="D57" s="52"/>
-      <c r="E57" s="52"/>
-      <c r="F57" s="52"/>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="52"/>
-      <c r="B58" s="52"/>
-      <c r="C58" s="52"/>
-      <c r="D58" s="52"/>
-      <c r="E58" s="52"/>
-      <c r="F58" s="52"/>
+      <c r="A56" s="4"/>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="4"/>
+      <c r="F56" s="53"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/mit_readme.xlsx
+++ b/mit_readme.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pavol\Desktop\Škola\mit_projekty\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A8AB4E2A-076D-4971-B3F9-F1ADCDB32820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6353FCFE-E87C-4E67-8CD8-6EFD8EAF5BE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16896" xr2:uid="{C8937BAE-C9A4-4CEB-A19F-3DAEC926D725}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="95">
   <si>
     <t>Predmet</t>
   </si>
@@ -213,9 +213,6 @@
     <t>FLP - Funkcionální a logické programování</t>
   </si>
   <si>
-    <t>RPL -   Parallel and Distributed Algorithms</t>
-  </si>
-  <si>
     <t>10 / 10</t>
   </si>
   <si>
@@ -252,15 +249,6 @@
     <t>Rozumné a zajímavé téma; chybí podrobnější technické detaily, působí spíše jako úvod do problematiky; příklady (videa) jsou dobré, ale omezené na jedinou scénu a přístup, hodila by se větší pestrost; chybí kvantitativní vyhodnocení přínosu; formální stránka slajdů a poznámek je rozumná.</t>
   </si>
   <si>
-    <t>PGR -   Computer Graphics</t>
-  </si>
-  <si>
-    <t>Didaktický ray-tracer v Pythonu – Physically Based Lighting</t>
-  </si>
-  <si>
-    <t>TODO</t>
-  </si>
-  <si>
     <t>POVa - Computer Vision</t>
   </si>
   <si>
@@ -319,6 +307,9 @@
   </si>
   <si>
     <t>Rotace obrazu</t>
+  </si>
+  <si>
+    <t>PRL -   Parallel and Distributed Algorithms</t>
   </si>
 </sst>
 </file>
@@ -1370,7 +1361,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C58E8B0-51CD-4485-AAB7-F2F9933D37DC}">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.21875" style="48" customWidth="1"/>
@@ -1742,14 +1733,14 @@
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="15" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="C27" s="8" t="s">
         <v>15</v>
       </c>
       <c r="D27" s="8"/>
       <c r="E27" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F27" s="34"/>
     </row>
@@ -1761,7 +1752,7 @@
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="8" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F28" s="34"/>
     </row>
@@ -1776,17 +1767,17 @@
     <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A30" s="5"/>
       <c r="B30" s="16" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>15</v>
       </c>
       <c r="D30" s="10"/>
       <c r="E30" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F30" s="50" t="s">
         <v>65</v>
-      </c>
-      <c r="F30" s="50" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1799,22 +1790,22 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B32" s="46" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C32" s="18" t="s">
         <v>15</v>
       </c>
       <c r="D32" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E32" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="F32" s="51" t="s">
         <v>69</v>
-      </c>
-      <c r="F32" s="51" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -1824,13 +1815,13 @@
         <v>16</v>
       </c>
       <c r="D33" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="E33" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="E33" s="8" t="s">
-        <v>72</v>
-      </c>
       <c r="F33" s="52" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -1844,20 +1835,18 @@
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C35" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="48" t="s">
+        <v>75</v>
+      </c>
+      <c r="E35" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E35" s="8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F35" s="34" t="s">
-        <v>77</v>
-      </c>
+      <c r="F35" s="34"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
@@ -1870,105 +1859,107 @@
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C37" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="48" t="s">
-        <v>79</v>
-      </c>
+      <c r="D37" s="8"/>
       <c r="E37" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F37" s="52" t="s">
         <v>80</v>
       </c>
-      <c r="F37" s="34"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="15"/>
-      <c r="C38" s="8"/>
+      <c r="C38" s="8" t="s">
+        <v>16</v>
+      </c>
       <c r="D38" s="8"/>
-      <c r="E38" s="8"/>
+      <c r="E38" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="F38" s="34"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
-      <c r="B39" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>15</v>
-      </c>
+      <c r="B39" s="15"/>
+      <c r="C39" s="8"/>
       <c r="D39" s="8"/>
-      <c r="E39" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="F39" s="52" t="s">
-        <v>84</v>
-      </c>
+      <c r="E39" s="8"/>
+      <c r="F39" s="34"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
-      <c r="B40" s="15"/>
+      <c r="B40" s="15" t="s">
+        <v>84</v>
+      </c>
       <c r="C40" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="D40" s="8"/>
+        <v>81</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>82</v>
+      </c>
       <c r="E40" s="8" t="s">
         <v>83</v>
       </c>
       <c r="F40" s="34"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="3"/>
-      <c r="B41" s="15"/>
-      <c r="C41" s="8"/>
-      <c r="D41" s="8"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="34"/>
+    <row r="41" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A41" s="5"/>
+      <c r="B41" s="16"/>
+      <c r="C41" s="10"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10"/>
+      <c r="F41" s="35"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="3"/>
-      <c r="B42" s="15" t="s">
+      <c r="A42" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="C42" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" s="48" t="s">
         <v>88</v>
       </c>
-      <c r="C42" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>86</v>
-      </c>
       <c r="E42" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="F42" s="56" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
+      <c r="C43" s="4"/>
+      <c r="D43" s="4"/>
+      <c r="E43" s="4"/>
+      <c r="F43" s="53"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="4"/>
+      <c r="B44" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F42" s="34"/>
-    </row>
-    <row r="43" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="5"/>
-      <c r="B43" s="16"/>
-      <c r="C43" s="10"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="10"/>
-      <c r="F43" s="35"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B44" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="D44" s="48" t="s">
+      <c r="C44" s="4">
+        <v>1</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="F44" s="54" t="s">
         <v>92</v>
-      </c>
-      <c r="E44" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F44" s="56" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -1981,21 +1972,11 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="4"/>
-      <c r="B46" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C46" s="4">
-        <v>1</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="F46" s="54" t="s">
-        <v>96</v>
-      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="4"/>
+      <c r="F46" s="53"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="4"/>
@@ -2061,22 +2042,6 @@
       <c r="E54" s="4"/>
       <c r="F54" s="53"/>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="4"/>
-      <c r="B55" s="4"/>
-      <c r="C55" s="4"/>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="53"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="4"/>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="53"/>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
